--- a/data_qr/2026-05-16.xlsx
+++ b/data_qr/2026-05-16.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BKP\Document BKP\Daily Reports\March 2026\May 17,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Desktop\my_first_website\data_qr\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10188"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>EthSwitch S.C.</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>BANK</t>
   </si>
 </sst>
 </file>
@@ -148,7 +151,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -340,7 +343,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -625,552 +628,554 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="E2:I35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="B1:F34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="19.44140625" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625"/>
-    <col min="13" max="13" width="11.6640625"/>
-    <col min="15" max="15" width="11.6640625"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375"/>
+    <col min="10" max="10" width="11.7109375"/>
+    <col min="12" max="12" width="11.7109375"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:9" ht="15.6">
-      <c r="E2" s="14" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="2:6" ht="15.75">
+      <c r="B1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+    </row>
+    <row r="2" spans="2:6" ht="15.75">
+      <c r="B2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
       <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-    </row>
-    <row r="3" spans="5:9" ht="15.6">
-      <c r="E3" s="14" t="s">
+    </row>
+    <row r="3" spans="2:6" ht="15.75">
+      <c r="B3" s="15">
+        <v>46159</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+    </row>
+    <row r="4" spans="2:6" ht="14.45" customHeight="1">
+      <c r="B4" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+    </row>
+    <row r="5" spans="2:6" ht="14.45" customHeight="1">
+      <c r="B5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="2:6" ht="16.5">
+      <c r="B6" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="16.5">
+      <c r="B7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>465</v>
+      </c>
+      <c r="E7" s="6">
+        <v>8</v>
+      </c>
+      <c r="F7" s="6">
+        <v>5291</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="16.5">
+      <c r="B8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1630</v>
+      </c>
+      <c r="D8" s="5">
+        <v>6520745.1299999999</v>
+      </c>
+      <c r="E8" s="6">
+        <v>146</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1056493</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="16.5">
+      <c r="B9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2251</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6">
+        <v>3355</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="16.5">
+      <c r="B10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="8">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>3300</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="16.5">
+      <c r="B11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="2:6" ht="16.5">
+      <c r="B12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="9">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5">
+        <v>3460</v>
+      </c>
+      <c r="E12" s="5">
         <v>1</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" spans="5:9" ht="15.6">
-      <c r="E4" s="15">
-        <v>46159</v>
-      </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-    </row>
-    <row r="5" spans="5:9" ht="14.4" customHeight="1">
-      <c r="E5" s="16" t="s">
+      <c r="F12" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="16.5">
+      <c r="B13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="5">
+        <v>352</v>
+      </c>
+      <c r="D13" s="5">
+        <v>6385170</v>
+      </c>
+      <c r="E13" s="6">
+        <v>213</v>
+      </c>
+      <c r="F13" s="6">
+        <v>1149316.0900000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="16.5">
+      <c r="B14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="5">
+        <v>77</v>
+      </c>
+      <c r="D14" s="5">
+        <v>98235.34</v>
+      </c>
+      <c r="E14" s="6">
+        <v>12</v>
+      </c>
+      <c r="F14" s="6">
+        <v>26276.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="16.5">
+      <c r="B15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="5">
+        <v>19</v>
+      </c>
+      <c r="D15" s="5">
+        <v>35605</v>
+      </c>
+      <c r="E15" s="6">
         <v>2</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-    </row>
-    <row r="6" spans="5:9" ht="14.4" customHeight="1">
-      <c r="E6" s="17"/>
-      <c r="F6" s="17" t="s">
+      <c r="F15" s="6">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="16.5">
+      <c r="B16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="5">
+        <v>238</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1102080.95</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1947</v>
+      </c>
+      <c r="F16" s="6">
+        <v>4868813.8600000003</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="16.5">
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="5">
+        <v>23</v>
+      </c>
+      <c r="D17" s="5">
+        <v>166584</v>
+      </c>
+      <c r="E17" s="6">
+        <v>23</v>
+      </c>
+      <c r="F17" s="6">
+        <v>30342.55</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="16.5">
+      <c r="B18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="5">
+        <v>78</v>
+      </c>
+      <c r="D18" s="5">
+        <v>413810</v>
+      </c>
+      <c r="E18" s="6">
+        <v>118</v>
+      </c>
+      <c r="F18" s="6">
+        <v>5501914.9000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="16.5">
+      <c r="B19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="5">
+        <v>82</v>
+      </c>
+      <c r="D19" s="5">
+        <v>140703.13</v>
+      </c>
+      <c r="E19" s="6">
+        <v>88</v>
+      </c>
+      <c r="F19" s="6">
+        <v>899144.65</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="16.5">
+      <c r="B20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="5">
+        <v>5</v>
+      </c>
+      <c r="D20" s="5">
+        <v>5900</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="16.5">
+      <c r="B21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="2:6" ht="16.5">
+      <c r="B22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="2:6" ht="16.5">
+      <c r="B23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="5">
+        <v>22</v>
+      </c>
+      <c r="D23" s="5">
+        <v>23444</v>
+      </c>
+      <c r="E23" s="6">
+        <v>49</v>
+      </c>
+      <c r="F23" s="6">
+        <v>1628426</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="16.5">
+      <c r="B24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="5">
+        <v>2</v>
+      </c>
+      <c r="D24" s="5">
+        <v>6.3</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" ht="16.5">
+      <c r="B25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="5">
+        <v>65</v>
+      </c>
+      <c r="D25" s="5">
+        <v>179888</v>
+      </c>
+      <c r="E25" s="6">
+        <v>14</v>
+      </c>
+      <c r="F25" s="6">
+        <v>8309.2999999999993</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="16.5">
+      <c r="B26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="10">
+        <v>4</v>
+      </c>
+      <c r="D26" s="5">
+        <v>2595</v>
+      </c>
+      <c r="E26" s="6">
+        <v>4</v>
+      </c>
+      <c r="F26" s="6">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" ht="16.5">
+      <c r="B27" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="10">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="16.5">
+      <c r="B28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="10">
+        <v>1</v>
+      </c>
+      <c r="D28" s="5">
+        <v>100</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" ht="16.5">
+      <c r="B29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="10">
+        <v>4</v>
+      </c>
+      <c r="D29" s="5">
+        <v>14850</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" ht="16.5">
+      <c r="B30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="11">
+        <v>7</v>
+      </c>
+      <c r="D30" s="5">
+        <v>4115</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" ht="16.5">
+      <c r="B31" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="12">
+        <v>1</v>
+      </c>
+      <c r="D31" s="6">
+        <v>550</v>
+      </c>
+      <c r="E31" s="6">
+        <v>2</v>
+      </c>
+      <c r="F31" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="16.5">
+      <c r="B32" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6">
+        <v>12</v>
+      </c>
+      <c r="F32" s="6">
+        <v>12650</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="16.5">
+      <c r="B33" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="9">
+        <v>24</v>
+      </c>
+      <c r="D33" s="5">
+        <v>116265</v>
+      </c>
+      <c r="E33" s="6">
         <v>3</v>
       </c>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="I6" s="17"/>
-    </row>
-    <row r="7" spans="5:9">
-      <c r="E7" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="5:9">
-      <c r="E8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="5">
-        <v>2</v>
-      </c>
-      <c r="G8" s="5">
-        <v>465</v>
-      </c>
-      <c r="H8" s="6">
-        <v>8</v>
-      </c>
-      <c r="I8" s="6">
-        <v>5291</v>
-      </c>
-    </row>
-    <row r="9" spans="5:9">
-      <c r="E9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="5">
-        <v>1630</v>
-      </c>
-      <c r="G9" s="5">
-        <v>6520745.1299999999</v>
-      </c>
-      <c r="H9" s="6">
-        <v>146</v>
-      </c>
-      <c r="I9" s="6">
-        <v>1056493</v>
-      </c>
-    </row>
-    <row r="10" spans="5:9">
-      <c r="E10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="8">
-        <v>2</v>
-      </c>
-      <c r="G10" s="5">
-        <v>2251</v>
-      </c>
-      <c r="H10" s="6">
-        <v>2</v>
-      </c>
-      <c r="I10" s="6">
-        <v>3355</v>
-      </c>
-    </row>
-    <row r="11" spans="5:9">
-      <c r="E11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="8">
-        <v>3</v>
-      </c>
-      <c r="G11" s="5">
-        <v>3300</v>
-      </c>
-      <c r="H11" s="6">
-        <v>0</v>
-      </c>
-      <c r="I11" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="5:9">
-      <c r="E12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="5:9">
-      <c r="E13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="9">
-        <v>5</v>
-      </c>
-      <c r="G13" s="5">
-        <v>3460</v>
-      </c>
-      <c r="H13" s="5">
-        <v>1</v>
-      </c>
-      <c r="I13" s="6">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="14" spans="5:9">
-      <c r="E14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="5">
-        <v>352</v>
-      </c>
-      <c r="G14" s="5">
-        <v>6385170</v>
-      </c>
-      <c r="H14" s="6">
-        <v>213</v>
-      </c>
-      <c r="I14" s="6">
-        <v>1149316.0900000001</v>
-      </c>
-    </row>
-    <row r="15" spans="5:9">
-      <c r="E15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="5">
-        <v>77</v>
-      </c>
-      <c r="G15" s="5">
-        <v>98235.34</v>
-      </c>
-      <c r="H15" s="6">
-        <v>12</v>
-      </c>
-      <c r="I15" s="6">
-        <v>26276.5</v>
-      </c>
-    </row>
-    <row r="16" spans="5:9">
-      <c r="E16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="5">
-        <v>19</v>
-      </c>
-      <c r="G16" s="5">
-        <v>35605</v>
-      </c>
-      <c r="H16" s="6">
-        <v>2</v>
-      </c>
-      <c r="I16" s="6">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="17" spans="5:9">
-      <c r="E17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="5">
-        <v>238</v>
-      </c>
-      <c r="G17" s="5">
-        <v>1102080.95</v>
-      </c>
-      <c r="H17" s="6">
-        <v>1947</v>
-      </c>
-      <c r="I17" s="6">
-        <v>4868813.8600000003</v>
-      </c>
-    </row>
-    <row r="18" spans="5:9">
-      <c r="E18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="5">
-        <v>23</v>
-      </c>
-      <c r="G18" s="5">
-        <v>166584</v>
-      </c>
-      <c r="H18" s="6">
-        <v>23</v>
-      </c>
-      <c r="I18" s="6">
-        <v>30342.55</v>
-      </c>
-    </row>
-    <row r="19" spans="5:9">
-      <c r="E19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="5">
-        <v>78</v>
-      </c>
-      <c r="G19" s="5">
-        <v>413810</v>
-      </c>
-      <c r="H19" s="6">
-        <v>118</v>
-      </c>
-      <c r="I19" s="6">
-        <v>5501914.9000000004</v>
-      </c>
-    </row>
-    <row r="20" spans="5:9">
-      <c r="E20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="5">
-        <v>82</v>
-      </c>
-      <c r="G20" s="5">
-        <v>140703.13</v>
-      </c>
-      <c r="H20" s="6">
-        <v>88</v>
-      </c>
-      <c r="I20" s="6">
-        <v>899144.65</v>
-      </c>
-    </row>
-    <row r="21" spans="5:9">
-      <c r="E21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="5">
-        <v>5</v>
-      </c>
-      <c r="G21" s="5">
-        <v>5900</v>
-      </c>
-      <c r="H21" s="6">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="22" spans="5:9">
-      <c r="E22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" spans="5:9">
-      <c r="E23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-    </row>
-    <row r="24" spans="5:9">
-      <c r="E24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="5">
-        <v>22</v>
-      </c>
-      <c r="G24" s="5">
-        <v>23444</v>
-      </c>
-      <c r="H24" s="6">
-        <v>49</v>
-      </c>
-      <c r="I24" s="6">
-        <v>1628426</v>
-      </c>
-    </row>
-    <row r="25" spans="5:9">
-      <c r="E25" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="5">
-        <v>2</v>
-      </c>
-      <c r="G25" s="5">
-        <v>6.3</v>
-      </c>
-      <c r="H25" s="6">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="5:9">
-      <c r="E26" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="5">
-        <v>65</v>
-      </c>
-      <c r="G26" s="5">
-        <v>179888</v>
-      </c>
-      <c r="H26" s="6">
-        <v>14</v>
-      </c>
-      <c r="I26" s="6">
-        <v>8309.2999999999993</v>
-      </c>
-    </row>
-    <row r="27" spans="5:9">
-      <c r="E27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="10">
-        <v>4</v>
-      </c>
-      <c r="G27" s="5">
-        <v>2595</v>
-      </c>
-      <c r="H27" s="6">
-        <v>4</v>
-      </c>
-      <c r="I27" s="6">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="28" spans="5:9">
-      <c r="E28" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="10">
-        <v>0</v>
-      </c>
-      <c r="G28" s="5">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6">
-        <v>1</v>
-      </c>
-      <c r="I28" s="6">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="29" spans="5:9">
-      <c r="E29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" s="10">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5">
-        <v>100</v>
-      </c>
-      <c r="H29" s="6">
-        <v>0</v>
-      </c>
-      <c r="I29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="5:9">
-      <c r="E30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="10">
-        <v>4</v>
-      </c>
-      <c r="G30" s="5">
-        <v>14850</v>
-      </c>
-      <c r="H30" s="6">
-        <v>0</v>
-      </c>
-      <c r="I30" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="5:9">
-      <c r="E31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F31" s="11">
-        <v>7</v>
-      </c>
-      <c r="G31" s="5">
-        <v>4115</v>
-      </c>
-      <c r="H31" s="6">
-        <v>0</v>
-      </c>
-      <c r="I31" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="5:9">
-      <c r="E32" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" s="12">
-        <v>1</v>
-      </c>
-      <c r="G32" s="6">
-        <v>550</v>
-      </c>
-      <c r="H32" s="6">
-        <v>2</v>
-      </c>
-      <c r="I32" s="6">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="33" spans="5:9">
-      <c r="E33" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="F33" s="6">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6">
-        <v>12</v>
-      </c>
-      <c r="I33" s="6">
-        <v>12650</v>
-      </c>
-    </row>
-    <row r="34" spans="5:9">
-      <c r="E34" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="9">
-        <v>24</v>
-      </c>
-      <c r="G34" s="5">
-        <v>116265</v>
-      </c>
-      <c r="H34" s="6">
-        <v>3</v>
-      </c>
-      <c r="I34" s="6">
         <v>2820</v>
       </c>
     </row>
-    <row r="35" spans="5:9">
-      <c r="E35" s="7" t="s">
+    <row r="34" spans="2:6" ht="16.5">
+      <c r="B34" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F35" s="13">
-        <f>SUM(F8:F34)</f>
+      <c r="C34" s="13">
+        <f>SUM(C7:C33)</f>
         <v>2646</v>
       </c>
-      <c r="G35" s="13">
-        <f>SUM(G8:G34)</f>
+      <c r="D34" s="13">
+        <f>SUM(D7:D33)</f>
         <v>15220122.85</v>
       </c>
-      <c r="H35" s="13">
-        <f>SUM(H8:H34)</f>
+      <c r="E34" s="13">
+        <f>SUM(E7:E33)</f>
         <v>2646</v>
       </c>
-      <c r="I35" s="13">
-        <f>SUM(I8:I34)</f>
-        <v>15220122.85</v>
+      <c r="F34" s="13">
+        <f>SUM(F7:F33)</f>
+        <v>15220122.850000001</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="K8:O29">
-    <sortCondition ref="K8"/>
+  <sortState ref="H8:L29">
+    <sortCondition ref="H8"/>
   </sortState>
   <mergeCells count="7">
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="E5:I5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/data_qr/2026-05-16.xlsx
+++ b/data_qr/2026-05-16.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>EthSwitch S.C.</t>
   </si>
@@ -40,7 +40,7 @@
     <t>QR Report</t>
   </si>
   <si>
-    <t>Successful QR Interoperable Transactions for May 17,2026</t>
+    <t>Successful QR Interoperable Transactions for May 16,2026</t>
   </si>
   <si>
     <t>As a Destination</t>
@@ -109,9 +109,6 @@
     <t>KAAFI</t>
   </si>
   <si>
-    <t>LIB</t>
-  </si>
-  <si>
     <t>M-PESA</t>
   </si>
   <si>
@@ -130,6 +127,9 @@
     <t>Siket</t>
   </si>
   <si>
+    <t>Tsedey Bank</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tsehay </t>
   </si>
   <si>
@@ -140,9 +140,6 @@
   </si>
   <si>
     <t>Total</t>
-  </si>
-  <si>
-    <t>BANK</t>
   </si>
 </sst>
 </file>
@@ -151,7 +148,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -165,32 +162,32 @@
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Century Gothic"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Century Gothic"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -198,13 +195,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -343,7 +340,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -662,7 +659,7 @@
     </row>
     <row r="3" spans="2:6" ht="15.75">
       <c r="B3" s="15">
-        <v>46159</v>
+        <v>46158</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
@@ -679,9 +676,7 @@
       <c r="F4" s="16"/>
     </row>
     <row r="5" spans="2:6" ht="14.45" customHeight="1">
-      <c r="B5" s="17" t="s">
-        <v>36</v>
-      </c>
+      <c r="B5" s="17"/>
       <c r="C5" s="17" t="s">
         <v>3</v>
       </c>
@@ -713,16 +708,16 @@
         <v>8</v>
       </c>
       <c r="C7" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D7" s="5">
-        <v>465</v>
+        <v>84490</v>
       </c>
       <c r="E7" s="6">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F7" s="6">
-        <v>5291</v>
+        <v>282437.5</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="16.5">
@@ -730,16 +725,16 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>1630</v>
+        <v>1596</v>
       </c>
       <c r="D8" s="5">
-        <v>6520745.1299999999</v>
+        <v>13256185.84</v>
       </c>
       <c r="E8" s="6">
-        <v>146</v>
+        <v>379</v>
       </c>
       <c r="F8" s="6">
-        <v>1056493</v>
+        <v>7890079.7400000002</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="16.5">
@@ -747,16 +742,16 @@
         <v>10</v>
       </c>
       <c r="C9" s="8">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D9" s="5">
-        <v>2251</v>
+        <v>43321</v>
       </c>
       <c r="E9" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F9" s="6">
-        <v>3355</v>
+        <v>300620</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="16.5">
@@ -764,42 +759,50 @@
         <v>11</v>
       </c>
       <c r="C10" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D10" s="5">
-        <v>3300</v>
+        <v>3302</v>
       </c>
       <c r="E10" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F10" s="6">
-        <v>0</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="16.5">
       <c r="B11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="C11" s="8">
+        <v>11</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1305</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="2:6" ht="16.5">
       <c r="B12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5">
-        <v>3460</v>
+        <v>25650</v>
       </c>
       <c r="E12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="6">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="16.5">
@@ -807,16 +810,16 @@
         <v>14</v>
       </c>
       <c r="C13" s="5">
-        <v>352</v>
+        <v>677</v>
       </c>
       <c r="D13" s="5">
-        <v>6385170</v>
+        <v>22527246</v>
       </c>
       <c r="E13" s="6">
-        <v>213</v>
+        <v>312</v>
       </c>
       <c r="F13" s="6">
-        <v>1149316.0900000001</v>
+        <v>3568510.17</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="16.5">
@@ -824,16 +827,16 @@
         <v>15</v>
       </c>
       <c r="C14" s="5">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="D14" s="5">
-        <v>98235.34</v>
+        <v>382794.99</v>
       </c>
       <c r="E14" s="6">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F14" s="6">
-        <v>26276.5</v>
+        <v>39860.01</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="16.5">
@@ -841,16 +844,16 @@
         <v>16</v>
       </c>
       <c r="C15" s="5">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="D15" s="5">
-        <v>35605</v>
+        <v>1946211</v>
       </c>
       <c r="E15" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6">
-        <v>430</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="16.5">
@@ -858,16 +861,16 @@
         <v>17</v>
       </c>
       <c r="C16" s="5">
-        <v>238</v>
+        <v>324</v>
       </c>
       <c r="D16" s="5">
-        <v>1102080.95</v>
+        <v>3752772.74</v>
       </c>
       <c r="E16" s="6">
-        <v>1947</v>
+        <v>2240</v>
       </c>
       <c r="F16" s="6">
-        <v>4868813.8600000003</v>
+        <v>5556550.1100000003</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="16.5">
@@ -875,16 +878,16 @@
         <v>18</v>
       </c>
       <c r="C17" s="5">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D17" s="5">
-        <v>166584</v>
+        <v>64767</v>
       </c>
       <c r="E17" s="6">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F17" s="6">
-        <v>30342.55</v>
+        <v>11669.52</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="16.5">
@@ -892,16 +895,16 @@
         <v>19</v>
       </c>
       <c r="C18" s="5">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="D18" s="5">
-        <v>413810</v>
+        <v>1105118</v>
       </c>
       <c r="E18" s="6">
-        <v>118</v>
+        <v>334</v>
       </c>
       <c r="F18" s="6">
-        <v>5501914.9000000004</v>
+        <v>16250917.02</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="16.5">
@@ -909,16 +912,16 @@
         <v>20</v>
       </c>
       <c r="C19" s="5">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="D19" s="5">
-        <v>140703.13</v>
+        <v>185169.3</v>
       </c>
       <c r="E19" s="6">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="F19" s="6">
-        <v>899144.65</v>
+        <v>5855095.7999999998</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="16.5">
@@ -929,48 +932,64 @@
         <v>5</v>
       </c>
       <c r="D20" s="5">
-        <v>5900</v>
+        <v>1580</v>
       </c>
       <c r="E20" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="6">
-        <v>240</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="16.5">
       <c r="B21" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
+      <c r="C21" s="5">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6">
+        <v>2000</v>
+      </c>
     </row>
     <row r="22" spans="2:6" ht="16.5">
       <c r="B22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="C22" s="5">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6">
+        <v>2</v>
+      </c>
+      <c r="F22" s="6">
+        <v>350</v>
+      </c>
     </row>
     <row r="23" spans="2:6" ht="16.5">
       <c r="B23" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D23" s="5">
-        <v>23444</v>
+        <v>46519</v>
       </c>
       <c r="E23" s="6">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="F23" s="6">
-        <v>1628426</v>
+        <v>4512215</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="16.5">
@@ -978,16 +997,16 @@
         <v>25</v>
       </c>
       <c r="C24" s="5">
-        <v>2</v>
+        <v>294</v>
       </c>
       <c r="D24" s="5">
-        <v>6.3</v>
+        <v>237999</v>
       </c>
       <c r="E24" s="6">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F24" s="6">
-        <v>0</v>
+        <v>18110</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="16.5">
@@ -995,16 +1014,16 @@
         <v>26</v>
       </c>
       <c r="C25" s="5">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="D25" s="5">
-        <v>179888</v>
+        <v>253826</v>
       </c>
       <c r="E25" s="6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F25" s="6">
-        <v>8309.2999999999993</v>
+        <v>12205</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="16.5">
@@ -1012,16 +1031,16 @@
         <v>27</v>
       </c>
       <c r="C26" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D26" s="5">
-        <v>2595</v>
+        <v>0</v>
       </c>
       <c r="E26" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="6">
-        <v>1120</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="16.5">
@@ -1029,16 +1048,16 @@
         <v>28</v>
       </c>
       <c r="C27" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E27" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="6">
-        <v>15000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="16.5">
@@ -1046,10 +1065,10 @@
         <v>29</v>
       </c>
       <c r="C28" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D28" s="5">
-        <v>100</v>
+        <v>26330</v>
       </c>
       <c r="E28" s="6">
         <v>0</v>
@@ -1063,10 +1082,10 @@
         <v>30</v>
       </c>
       <c r="C29" s="10">
-        <v>4</v>
+        <v>109</v>
       </c>
       <c r="D29" s="5">
-        <v>14850</v>
+        <v>290274</v>
       </c>
       <c r="E29" s="6">
         <v>0</v>
@@ -1080,16 +1099,16 @@
         <v>31</v>
       </c>
       <c r="C30" s="11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D30" s="5">
-        <v>4115</v>
+        <v>0</v>
       </c>
       <c r="E30" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="16.5">
@@ -1097,16 +1116,16 @@
         <v>32</v>
       </c>
       <c r="C31" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="6">
-        <v>550</v>
+        <v>36000</v>
       </c>
       <c r="E31" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F31" s="6">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:6" ht="16.5">
@@ -1120,10 +1139,10 @@
         <v>0</v>
       </c>
       <c r="E32" s="6">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F32" s="6">
-        <v>12650</v>
+        <v>321795</v>
       </c>
     </row>
     <row r="33" spans="2:6" ht="16.5">
@@ -1131,16 +1150,16 @@
         <v>34</v>
       </c>
       <c r="C33" s="9">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D33" s="5">
-        <v>116265</v>
+        <v>425966</v>
       </c>
       <c r="E33" s="6">
         <v>3</v>
       </c>
       <c r="F33" s="6">
-        <v>2820</v>
+        <v>727</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="16.5">
@@ -1149,19 +1168,19 @@
       </c>
       <c r="C34" s="13">
         <f>SUM(C7:C33)</f>
-        <v>2646</v>
+        <v>3691</v>
       </c>
       <c r="D34" s="13">
         <f>SUM(D7:D33)</f>
-        <v>15220122.85</v>
+        <v>44696836.870000005</v>
       </c>
       <c r="E34" s="13">
         <f>SUM(E7:E33)</f>
-        <v>2646</v>
+        <v>3691</v>
       </c>
       <c r="F34" s="13">
         <f>SUM(F7:F33)</f>
-        <v>15220122.850000001</v>
+        <v>44696836.869999997</v>
       </c>
     </row>
   </sheetData>
